--- a/docs/sp_ui_engineer/HILDA_SP_Schema.xlsx
+++ b/docs/sp_ui_engineer/HILDA_SP_Schema.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -516,7 +516,7 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>This workbook is the authoritative HILDA-side view of all 8 SharePoint Lists in the DeliverableHub SP site. The SP UI engineer uses it to build SP list schemas, Choice values, forms and classic web parts. The HILDA architect uses it to validate that customer YAML mappings stay consistent. It supersedes ad-hoc field discussions; if a field is not in this workbook it is not in HILDA's contract.</t>
+          <t>This workbook is the authoritative HILDA-side view of all 7 SharePoint Lists (was 8; TGGroups removed per [D-051] impl note 2026-06-12 - TG fields denormalized onto DeliveryItems) in the DeliverableHub SP site. The SP UI engineer uses it to build SP list schemas, Choice values, forms and classic web parts. The HILDA architect uses it to validate that customer YAML mappings stay consistent. It supersedes ad-hoc field discussions; if a field is not in this workbook it is not in HILDA's contract.</t>
         </is>
       </c>
     </row>
@@ -658,6 +658,20 @@
   - core/src/template_schema/MODULE.md (canonical enums)
   - docs/compact/requirements.md (Ph-2 markers)
   - docs/compact/DECISIONS.md [D-051] [D-052] [D-053] [D-054] [D-055] [D-060] [D-063]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12 amendments</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>D-073: SP UI engineer manually provisions SP lists from this workbook + customizations/sharepoint_config/&lt;customer_slug&gt;.yaml; HILDA does NOT call REST to create lists (corp SP-2017 SP-alert + custom-task constraint). [D-051] impl note 2026-06-12 (D-DRAFT-Y): TGGroups removed as separate SP list; 9 TG fields denormalized onto DeliveryItems as SP-side READ-ONLY mirrors (YAML source-of-truth). D-074: SP UI consumes HILDA via top-level browser navigation (link-out to HILDA-rendered pages), NOT SP-side cross-origin XHR. Schema deltas absorbed: is_milestone_gating rename (was milestone_gating); item_no immutability Invariant (referential integrity for FR-77); pm_approval_at + pm_approval_pm_id per [D-068]; owner_corp_id on Users + DeliveryItems; default_work_item_config moved to YAML (not in SP); source_system dropped (channel column covers); last_updated dropped (use SP built-in Modified); folder_routing_template_id dropped (templates not reused across TGs); SP system columns (Created/Modified/Author/Editor) NOT duplicated as custom columns; ingress_nsd Choice: none/nsd1/nsd2.</t>
         </is>
       </c>
     </row>
@@ -695,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1440,50 +1454,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>source_system</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>source_system</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>source_system</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr"/>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Ph-2</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>User prompt</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>???  Origin system identifier (e.g., 'gmail-corp', 'plm-prod'). Not explicit in REQUIREMENTS.md §2.7. OPEN ITEM — confirm with HILDA team.</t>
-        </is>
-      </c>
-    </row>
+    <row r="19" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
@@ -1943,7 +1914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -3435,17 +3406,17 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>milestone_gating</t>
+          <t>is_milestone_gating</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>milestone_gating</t>
+          <t>is_milestone_gating</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>milestone_gating</t>
+          <t>is_milestone_gating</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -3467,12 +3438,12 @@
       <c r="H35" s="6" t="inlineStr"/>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>§2.4 / §12 #1</t>
+          <t>D-074; template_schema/MODULE.md Invariant 2026-06-12; FR-64 enablement</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>???  Field name TBD — prototype may use 'MilestoneGating'. Does this item gate milestone closure? OPEN ITEM §12 #1.</t>
+          <t>Renamed 2026-06-12 from milestone_gating per SP UI engineer 2026-06-10 review. Boolean flag indicating whether this item gates milestone closure (FR-64 Close All Items enablement).</t>
         </is>
       </c>
     </row>
@@ -3655,17 +3626,17 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>last_updated</t>
+          <t>last_owner_contacted</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>last_updated</t>
+          <t>last_owner_contacted</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>last_updated</t>
+          <t>last_owner_contacted</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -3676,7 +3647,7 @@
       <c r="E40" s="6" t="inlineStr"/>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -3690,26 +3661,22 @@
           <t>§2.4</t>
         </is>
       </c>
-      <c r="J40" s="6" t="inlineStr">
-        <is>
-          <t>Auto-updated on every modification. SP standard 'Modified' may serve; HILDA expects this canonical name — alias if needed.</t>
-        </is>
-      </c>
+      <c r="J40" s="6" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>last_owner_contacted</t>
+          <t>last_reminder_triggered_at</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>last_owner_contacted</t>
+          <t>last_reminder_triggered_at</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>last_owner_contacted</t>
+          <t>last_reminder_triggered_at</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -3731,74 +3698,78 @@
       <c r="H41" s="6" t="inlineStr"/>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>§2.4</t>
-        </is>
-      </c>
-      <c r="J41" s="6" t="inlineStr"/>
+          <t>§2.4 / §4.6</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>Set by §4.6 Send Reminder button. SP alert → action_type = send_reminder.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>last_reminder_triggered_at</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>last_reminder_triggered_at</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>last_reminder_triggered_at</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>DateTime</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr"/>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>force_tracking_enabled</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>force_tracking_enabled</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>force_tracking_enabled</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr"/>
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>Ph-1</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr"/>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>§2.4 / §4.6</t>
-        </is>
-      </c>
-      <c r="J42" s="6" t="inlineStr">
-        <is>
-          <t>Set by §4.6 Send Reminder button. SP alert → action_type = send_reminder.</t>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>Ph-2</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>docs/compact/requirements.md / FR-81</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>Per-item override of TGGroups.tracking_enabled. When set, takes precedence.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>force_tracking_enabled</t>
+          <t>per_item_rule_overrides</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>force_tracking_enabled</t>
+          <t>per_item_rule_overrides</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>force_tracking_enabled</t>
+          <t>per_item_rule_overrides</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr"/>
@@ -3815,56 +3786,560 @@
       <c r="H43" s="7" t="inlineStr"/>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>docs/compact/requirements.md / FR-81</t>
+          <t>FR-31 Ph-2</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>Per-item override of TGGroups.tracking_enabled. When set, takes precedence.</t>
+          <t>JSON object — per-item rule parameter overrides (LastContactThreshold N, DeadlineProximity N, reminder template, etc). Editable via FR-31 control panel.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>per_item_rule_overrides</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>per_item_rule_overrides</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>per_item_rule_overrides</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>pm_approval_at</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>pm_approval_at</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>pm_approval_at</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Ph-1</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr"/>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>[D-068] PM-approval recording; FR-28 PMApproval trigger</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>Added 2026-06-12 per [D-068]. Set by workflow_engine PMApproval task body BEFORE tracker.update_delivery_state(target=ReadyForSubmission); cleared per [D-067] rewind path. SP alert subscription on this field change required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>pm_approval_pm_id</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>pm_approval_pm_id</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>pm_approval_pm_id</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Ph-1</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr"/>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>[D-068]</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>Added 2026-06-12 per [D-068]. PM/TPM attribution for the PMApproval action (User-typed in SP). Cleared together with pm_approval_at.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>owner_corp_id</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>owner_corp_id</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>owner_corp_id</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Ph-1</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr"/>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>D-073 / SP UI engineer 2026-06-10</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>Added 2026-06-12. Denormalized from Users.owner_corp_id at DI creation; used by corp messenger Ph-2 (replaces dropped user_corp_messenger_handle).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>tg_name_denorm</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>tg_name_denorm</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>tg_name_denorm</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr"/>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>Ph-1</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr"/>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>[D-051] impl note 2026-06-12 (TGGroups denormalized)</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>Denormalization marker row. The tg_name column on DI rows (row 9 above) IS the denormalized TG identifier. This row exists for inventory completeness of the 9 TG-field denormalization set per D-DRAFT-Y; in practice the row 9 tg_name column does double duty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>ingress_nsd</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>ingress_nsd</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>ingress_nsd</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>none, nsd1, nsd2</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>Ph-1</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>[D-051] impl note 2026-06-12; SP UI engineer 2026-06-10</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>NEW 2026-06-12. Denormalized from TGGroupBase. SP-side READ-ONLY mirror (TPM SP UI must not allow editing TG columns on DI rows); YAML source-of-truth at customizations/template_schemas/&lt;customer_slug&gt;/tg_groups.yaml. Choice: none / nsd1 / nsd2 per SP UI engineer 2026-06-10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>tracking_modality_tg</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>tracking_modality_tg</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>tracking_modality_tg</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>MultiChoice</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Email, CorporateMessenger, CorporatePLM, NetworkSharedDrive, CustomerJIRA</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>Ph-1</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr"/>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>[D-051] impl note 2026-06-12; [D-037]</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>NEW 2026-06-12. Denormalized TG-level tracking_modality from TGGroupBase. Distinct column name from row 23 tracking_modality (per-item) to avoid name collision in SP. SP-side READ-ONLY mirror.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>email_group_alias</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>email_group_alias</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>email_group_alias</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr"/>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Ph-1</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr"/>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>[D-051] impl note 2026-06-12</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>NEW 2026-06-12. Denormalized from TGGroupBase. TG corporate email distribution alias. SP-side READ-ONLY mirror.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>tg_owner_name</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>tg_owner_name</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>tg_owner_name</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr"/>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>Ph-1</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr"/>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>[D-051] impl note 2026-06-12</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>NEW 2026-06-12. Denormalized from TGGroupBase. TG coordinator name; distinct from per-item owner_name. SP-side READ-ONLY mirror.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>tg_owner_email</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>tg_owner_email</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>tg_owner_email</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr"/>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>Ph-1</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr"/>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>[D-051] impl note 2026-06-12</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>NEW 2026-06-12. Denormalized from TGGroupBase. SP-side READ-ONLY mirror.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>default_cc_list</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>default_cc_list</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>default_cc_list</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr"/>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>Ph-2</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>FR-31 Ph-2</t>
-        </is>
-      </c>
-      <c r="J44" s="7" t="inlineStr">
-        <is>
-          <t>JSON object — per-item rule parameter overrides (LastContactThreshold N, DeadlineProximity N, reminder template, etc). Editable via FR-31 control panel.</t>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>Ph-1</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr"/>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>[D-051] impl note 2026-06-12</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>NEW 2026-06-12. Denormalized from TGGroupBase. Per-TG default CC list (JSON Note). SP-side READ-ONLY mirror.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>folder_routing_enabled</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>folder_routing_enabled</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>folder_routing_enabled</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr"/>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>Ph-1</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>[D-051] impl note 2026-06-12</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>NEW 2026-06-12. Denormalized from TGGroupBase. FR-77 Type-2 routing enablement. SP-side READ-ONLY mirror.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>tracking_enabled</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>tracking_enabled</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>tracking_enabled</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr"/>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>Ph-1</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>[D-051] impl note 2026-06-12</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>NEW 2026-06-12. Denormalized from TGGroupBase. FR-81 enablement. SP-side READ-ONLY mirror.</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -4900,54 +5375,11 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>???  Field name TBD per §12 #3. Suggested per §4.4: hidden field set by Close All Items button. OPEN ITEM — confirm with HILDA team.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>default_work_item_config</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>default_work_item_config</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>default_work_item_config</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Ph-1</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>FR-78 / template_schema</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>JSON — full-replacement config for the auto-instantiated default work-item per FR-78. Pydantic type DefaultWorkItemConfig on HILDA side. Populated at tracker creation.</t>
-        </is>
-      </c>
-    </row>
+          <t>SP-side ONLY field per SP UI engineer 2026-06-10; NO HILDA Postgres mirror (SP is system-of-record for this audit timestamp). FR-64 Close All Items action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
@@ -5499,7 +5931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -5517,14 +5949,14 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>SP List: TGGroups</t>
+          <t>YAML schema reference (NOT a SP list): TGGroups</t>
         </is>
       </c>
     </row>
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Per-(milestone, tg_name) Technical Group metadata. Lookup target for the TG-header rendering in §3.1. Unique constraint: (milestone_id, tg_name).</t>
+          <t>NOT a SP list per [D-051] impl note 2026-06-12 (D-DRAFT-Y) - TGGroups removed as separate SP list; TG fields denormalized onto DeliveryItems (see DeliveryItems tab rows for ingress_nsd, tracking_modality_tg, email_group_alias, tg_owner_name, tg_owner_email, default_cc_list, folder_routing_enabled, tracking_enabled, plus the existing tg_name column at row 9). This tab retained as YAML schema reference documenting TGGroupBase Pydantic model fields (source-of-truth at customizations/template_schemas/&lt;customer_slug&gt;/tg_groups.yaml per template_schema/MODULE.md). SP UI engineer does NOT create a TGGroups SP list.</t>
         </is>
       </c>
     </row>
@@ -5955,7 +6387,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>NSD1, NSD2</t>
+          <t>none, nsd1, nsd2</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -5980,7 +6412,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Dual-NSD topology — which NSD this TG's documents arrive on (relevant when DeliveryItems.tracking_modality includes NetworkSharedDrive). Added 2026-06-09.</t>
+          <t>Choice values updated 2026-06-12 per SP UI engineer 2026-06-10 (was NSD1/NSD2; 'none' added).</t>
         </is>
       </c>
     </row>
@@ -6080,50 +6512,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>folder_routing_template_id</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>folder_routing_template_id</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>folder_routing_template_id</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Ph-2</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr"/>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>FR-77 Ph-2</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>???  Reference to a folder-routing template — Ph-2 extension. OPEN ITEM — confirm with HILDA team.</t>
-        </is>
-      </c>
-    </row>
+    <row r="15" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
@@ -6139,7 +6528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -6440,6 +6829,50 @@
       </c>
       <c r="J8" s="6" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>owner_corp_id</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>owner_corp_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>owner_corp_id</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Ph-1</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>SP UI engineer 2026-06-10 / D-073</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>NEW 2026-06-12. Canonical per-person corp ID. Reused by corp messenger Ph-2 (replaces dropped user_corp_messenger_handle per user 2026-06-12).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>

--- a/docs/sp_ui_engineer/HILDA_SP_Schema.xlsx
+++ b/docs/sp_ui_engineer/HILDA_SP_Schema.xlsx
@@ -5338,17 +5338,17 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>close_all_triggered_at</t>
+          <t>close_all_items_triggered_at</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>close_all_triggered_at</t>
+          <t>close_all_items_triggered_at</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>close_all_triggered_at</t>
+          <t>close_all_items_triggered_at</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">

--- a/docs/sp_ui_engineer/HILDA_SP_Schema.xlsx
+++ b/docs/sp_ui_engineer/HILDA_SP_Schema.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CommunicationLog" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DeliveryItems" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Devices" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PMCredentials" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TGGroups" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Users" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CommunicationLog" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Customers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DeliveryItems" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Devices" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Milestones" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="PMCredentials" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TGGroups" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Users" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1495,7 +1495,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Per-customer (carrier) metadata. One row per carrier.</t>
+          <t>Per-customer (carrier) metadata. One row per carrier. | D-DRAFT-Z 2026-06-12: SP UI engineer display surface only; HILDA does NOT read this list at runtime — customer data sourced from customizations/template_schemas/&lt;customer_slug&gt;/customer.yaml at HILDA startup</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>One row per connected device under certification. Drives §3.2 Device Tracker + §3.3 PM Dashboard views.</t>
+          <t>One row per connected device under certification. Drives §3.2 Device Tracker + §3.3 PM Dashboard views. | D-DRAFT-Z 2026-06-12: SP UI engineer display surface only; HILDA does NOT read this list at runtime — device data sourced from customer.yaml devices: sub-block</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -5379,7 +5379,94 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>customer_slug</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>customer_slug</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>customer_slug</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Ph-1</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>D-DRAFT-Z 2026-06-12 (HILDA runtime SP coupling restricted to Milestones + DeliveryItems lists)</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>READ-ONLY mirror per D-DRAFT-Z; denormalized from customizations/template_schemas/&lt;customer_slug&gt;/customer.yaml at HILDA startup. HILDA reads this from Milestone row at runtime instead of joining Customers SP list. TPM SP UI must not allow editing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>device_slug</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>device_slug</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>device_slug</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Ph-1</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr"/>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>D-DRAFT-Z 2026-06-12</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>READ-ONLY mirror per D-DRAFT-Z; denormalized from customer.yaml devices: sub-block at HILDA startup. HILDA reads from Milestone row at runtime instead of joining Devices SP list. TPM SP UI must not allow editing.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
@@ -5420,7 +5507,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Metadata only — no plaintext secrets ever live here. HILDA holds the encrypted blob outside SP. Phase-3+ — list provisioning can wait but column shape locked here for HILDA REST client compat.</t>
+          <t>Metadata only — no plaintext secrets ever live here. HILDA holds the encrypted blob outside SP. Phase-3+ — list provisioning can wait but column shape locked here for HILDA REST client compat. | D-DRAFT-Z 2026-06-12: SP UI engineer display surface only; HILDA does NOT read this list at runtime — credentials live in HILDA-local credential_service per [D-019] / [D-038]; HILDA reads via get_credential() not via SP</t>
         </is>
       </c>
     </row>
@@ -6553,7 +6640,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Corp users — PMs, TPMs, Team Leads, Admins. Drives permissions and Devices.assigned_pm_id.</t>
+          <t>Corp users — PMs, TPMs, Team Leads, Admins. Drives permissions and Devices.assigned_pm_id. | D-DRAFT-Z 2026-06-12: SP UI engineer display surface only; HILDA does NOT read this list at runtime — owner identity denormalized onto DeliveryItem rows per FR-2 owner identity model 2026-06-12; HILDA reads from DI rows, not Users list</t>
         </is>
       </c>
     </row>
